--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_diff</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_diff</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_diff</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_diff</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_diff</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_diff</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_diff</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_diff</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_diff</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_diff</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_diff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_diff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_diff</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_diff</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_diff</t>
         </is>
@@ -443,49 +448,52 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.02406972128985019</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.03426239021457855</v>
+        <v>0.02406972126101475</v>
       </c>
       <c r="D2">
-        <v>0.04445603739042081</v>
+        <v>0.0342623902501441</v>
       </c>
       <c r="E2">
-        <v>0.05342272425563743</v>
+        <v>0.04445603734473524</v>
       </c>
       <c r="F2">
-        <v>0.09808964774124462</v>
+        <v>0.05342272423991234</v>
       </c>
       <c r="G2">
-        <v>0.0835509555362115</v>
+        <v>0.09808964773794926</v>
       </c>
       <c r="H2">
-        <v>0.09896259100269533</v>
+        <v>0.08355095521648082</v>
       </c>
       <c r="I2">
-        <v>0.1395383528824401</v>
+        <v>0.09896259082934877</v>
       </c>
       <c r="J2">
-        <v>0.1343347262181672</v>
+        <v>0.1395383529910919</v>
       </c>
       <c r="K2">
-        <v>0.1598224672891664</v>
+        <v>0.1343347268131432</v>
       </c>
       <c r="L2">
-        <v>0.1864755544499948</v>
+        <v>0.1598224671429355</v>
       </c>
       <c r="M2">
-        <v>0.2392661665138228</v>
+        <v>0.1864755538846821</v>
       </c>
       <c r="N2">
-        <v>0.3238305742040932</v>
+        <v>0.239266163183007</v>
       </c>
       <c r="O2">
-        <v>0.3958089667065677</v>
+        <v>0.3238305777377158</v>
       </c>
       <c r="P2">
-        <v>0.4326417408982691</v>
+        <v>0.395808976886688</v>
+      </c>
+      <c r="Q2">
+        <v>0.4326417416725999</v>
       </c>
     </row>
     <row r="3">
@@ -495,49 +503,52 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.0388846288186861</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.03594244399979163</v>
+        <v>0.03888462822637945</v>
       </c>
       <c r="D3">
-        <v>0.06488134317380045</v>
+        <v>0.03594244326911089</v>
       </c>
       <c r="E3">
-        <v>0.1579600492643117</v>
+        <v>0.06488134268398438</v>
       </c>
       <c r="F3">
-        <v>0.1404950385839135</v>
+        <v>0.1579600427071743</v>
       </c>
       <c r="G3">
-        <v>0.1692426840139705</v>
+        <v>0.1404950374348409</v>
       </c>
       <c r="H3">
-        <v>0.2368901706469027</v>
+        <v>0.1692426819768151</v>
       </c>
       <c r="I3">
-        <v>0.2714398011297819</v>
+        <v>0.2368901668104566</v>
       </c>
       <c r="J3">
-        <v>0.337965781686665</v>
+        <v>0.271439797899279</v>
       </c>
       <c r="K3">
-        <v>0.3726480446080134</v>
+        <v>0.3379657692435547</v>
       </c>
       <c r="L3">
-        <v>0.4234366758773169</v>
+        <v>0.3726480110774195</v>
       </c>
       <c r="M3">
-        <v>0.4786576932975436</v>
+        <v>0.423436608168691</v>
       </c>
       <c r="N3">
-        <v>0.5335883417339022</v>
+        <v>0.4786575932570324</v>
       </c>
       <c r="O3">
-        <v>0.5466065230314199</v>
+        <v>0.5335881840053656</v>
       </c>
       <c r="P3">
-        <v>0.5400277007421661</v>
+        <v>0.5466063617337388</v>
+      </c>
+      <c r="Q3">
+        <v>0.5400275370764285</v>
       </c>
     </row>
     <row r="4">
@@ -547,49 +558,52 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.02198725168221061</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.03316854925031909</v>
+        <v>0.02198725166647436</v>
       </c>
       <c r="D4">
-        <v>0.04275905706128202</v>
+        <v>0.03316854926956492</v>
       </c>
       <c r="E4">
-        <v>0.06084537731224282</v>
+        <v>0.04275905693612603</v>
       </c>
       <c r="F4">
-        <v>0.09079041488296091</v>
+        <v>0.06084537714932048</v>
       </c>
       <c r="G4">
-        <v>0.08295622735897934</v>
+        <v>0.09079041423824219</v>
       </c>
       <c r="H4">
-        <v>0.09297182380011093</v>
+        <v>0.08295622881483444</v>
       </c>
       <c r="I4">
-        <v>0.1180087296309373</v>
+        <v>0.09297182443273733</v>
       </c>
       <c r="J4">
-        <v>0.1606593729886414</v>
+        <v>0.1180087302988089</v>
       </c>
       <c r="K4">
-        <v>0.2089456986583658</v>
+        <v>0.160659375282763</v>
       </c>
       <c r="L4">
-        <v>0.2488809051105881</v>
+        <v>0.2089457033541128</v>
       </c>
       <c r="M4">
-        <v>0.3290330368604316</v>
+        <v>0.2488809157010321</v>
       </c>
       <c r="N4">
-        <v>0.3921627630312524</v>
+        <v>0.3290330457201749</v>
       </c>
       <c r="O4">
-        <v>0.4359953435539586</v>
+        <v>0.3921627678006898</v>
       </c>
       <c r="P4">
-        <v>0.4848319505270974</v>
+        <v>0.4359953467169128</v>
+      </c>
+      <c r="Q4">
+        <v>0.4848319423374215</v>
       </c>
     </row>
     <row r="5">
@@ -599,49 +613,52 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.01950234127783956</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.04741195363891548</v>
+        <v>0.01950234122075734</v>
       </c>
       <c r="D5">
-        <v>0.05907066622014279</v>
+        <v>0.04741195320577651</v>
       </c>
       <c r="E5">
-        <v>0.09695535262248411</v>
+        <v>0.05907066570830588</v>
       </c>
       <c r="F5">
-        <v>0.1164318029581017</v>
+        <v>0.09695535190211135</v>
       </c>
       <c r="G5">
-        <v>0.1301342591242648</v>
+        <v>0.1164318025466525</v>
       </c>
       <c r="H5">
-        <v>0.1554241169158169</v>
+        <v>0.1301342570819596</v>
       </c>
       <c r="I5">
-        <v>0.2164452196284936</v>
+        <v>0.1554241154405082</v>
       </c>
       <c r="J5">
-        <v>0.3136746984108985</v>
+        <v>0.2164452127704739</v>
       </c>
       <c r="K5">
-        <v>0.370666452592122</v>
+        <v>0.3136746981122614</v>
       </c>
       <c r="L5">
-        <v>0.4288372547211173</v>
+        <v>0.3706664599709263</v>
       </c>
       <c r="M5">
-        <v>0.4517149035017631</v>
+        <v>0.4288372618168326</v>
       </c>
       <c r="N5">
-        <v>0.4609272023427946</v>
+        <v>0.4517149090756221</v>
       </c>
       <c r="O5">
-        <v>0.4699514741428964</v>
+        <v>0.4609271982246932</v>
       </c>
       <c r="P5">
-        <v>0.4832810677281704</v>
+        <v>0.4699514682291456</v>
+      </c>
+      <c r="Q5">
+        <v>0.4832810639585653</v>
       </c>
     </row>
     <row r="6">
@@ -651,49 +668,52 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.02059155683042346</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.04572563489711789</v>
+        <v>0.02059155679040026</v>
       </c>
       <c r="D6">
-        <v>0.05706032984645237</v>
+        <v>0.04572563468251012</v>
       </c>
       <c r="E6">
-        <v>0.09123833449097407</v>
+        <v>0.05706032943373085</v>
       </c>
       <c r="F6">
-        <v>0.09564130908555879</v>
+        <v>0.09123833409715509</v>
       </c>
       <c r="G6">
-        <v>0.1082335672850303</v>
+        <v>0.09564130778556124</v>
       </c>
       <c r="H6">
-        <v>0.1541882768483999</v>
+        <v>0.1082335662283257</v>
       </c>
       <c r="I6">
-        <v>0.1967254774191847</v>
+        <v>0.1541882736858077</v>
       </c>
       <c r="J6">
-        <v>0.2415784620503366</v>
+        <v>0.1967254741645829</v>
       </c>
       <c r="K6">
-        <v>0.2714732226949074</v>
+        <v>0.2415784662497825</v>
       </c>
       <c r="L6">
-        <v>0.3205686517562806</v>
+        <v>0.2714732337111453</v>
       </c>
       <c r="M6">
-        <v>0.3570266476025046</v>
+        <v>0.3205686700392462</v>
       </c>
       <c r="N6">
-        <v>0.394726922382242</v>
+        <v>0.3570266595698545</v>
       </c>
       <c r="O6">
-        <v>0.4098764594844488</v>
+        <v>0.3947269422811922</v>
       </c>
       <c r="P6">
-        <v>0.4357556404412128</v>
+        <v>0.4098764750607388</v>
+      </c>
+      <c r="Q6">
+        <v>0.4357556506860989</v>
       </c>
     </row>
     <row r="7">
@@ -703,49 +723,52 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.02481144046563599</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.03223677318485185</v>
+        <v>0.02481144044761385</v>
       </c>
       <c r="D7">
-        <v>0.04734018657056083</v>
+        <v>0.03223677322310559</v>
       </c>
       <c r="E7">
-        <v>0.05076836151083119</v>
+        <v>0.04734018640112991</v>
       </c>
       <c r="F7">
-        <v>0.07563573018825298</v>
+        <v>0.05076836139153074</v>
       </c>
       <c r="G7">
-        <v>0.07321578715502775</v>
+        <v>0.07563572984106959</v>
       </c>
       <c r="H7">
-        <v>0.09853501978991774</v>
+        <v>0.0732157870721527</v>
       </c>
       <c r="I7">
-        <v>0.1144640362054218</v>
+        <v>0.09853502015587989</v>
       </c>
       <c r="J7">
-        <v>0.1474389148888284</v>
+        <v>0.1144640381551062</v>
       </c>
       <c r="K7">
-        <v>0.1844828186869123</v>
+        <v>0.1474389170510418</v>
       </c>
       <c r="L7">
-        <v>0.2301401280329914</v>
+        <v>0.1844828235220124</v>
       </c>
       <c r="M7">
-        <v>0.3083019758713003</v>
+        <v>0.2301401392351334</v>
       </c>
       <c r="N7">
-        <v>0.364939712085687</v>
+        <v>0.3083019960850337</v>
       </c>
       <c r="O7">
-        <v>0.4277422630775481</v>
+        <v>0.3649397257964595</v>
       </c>
       <c r="P7">
-        <v>0.4667065766241868</v>
+        <v>0.4277422675841482</v>
+      </c>
+      <c r="Q7">
+        <v>0.4667065877423366</v>
       </c>
     </row>
     <row r="8">
@@ -755,49 +778,52 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.02124766125200217</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.03140045511519918</v>
+        <v>0.0212476612616429</v>
       </c>
       <c r="D8">
-        <v>0.04974637815669458</v>
+        <v>0.03140045511863898</v>
       </c>
       <c r="E8">
-        <v>0.06510565304718807</v>
+        <v>0.04974637798667703</v>
       </c>
       <c r="F8">
-        <v>0.06624618214523903</v>
+        <v>0.06510565277588742</v>
       </c>
       <c r="G8">
-        <v>0.1054287867503693</v>
+        <v>0.06624618208517874</v>
       </c>
       <c r="H8">
-        <v>0.1149101599161206</v>
+        <v>0.1054287869006096</v>
       </c>
       <c r="I8">
-        <v>0.1616046913590283</v>
+        <v>0.1149101601784935</v>
       </c>
       <c r="J8">
-        <v>0.2214257648931273</v>
+        <v>0.1616046919375265</v>
       </c>
       <c r="K8">
-        <v>0.259989506678036</v>
+        <v>0.2214257699802955</v>
       </c>
       <c r="L8">
-        <v>0.292219960582506</v>
+        <v>0.2599895154744388</v>
       </c>
       <c r="M8">
-        <v>0.343525218930351</v>
+        <v>0.2922199823157025</v>
       </c>
       <c r="N8">
-        <v>0.4207624179732662</v>
+        <v>0.3435252522289001</v>
       </c>
       <c r="O8">
-        <v>0.4870764056828214</v>
+        <v>0.4207624448287999</v>
       </c>
       <c r="P8">
-        <v>0.5321114739082707</v>
+        <v>0.4870764172296881</v>
+      </c>
+      <c r="Q8">
+        <v>0.532111470880379</v>
       </c>
     </row>
     <row r="9">
@@ -807,49 +833,52 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.02252751089146088</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.03383559462275876</v>
+        <v>0.02252751089759303</v>
       </c>
       <c r="D9">
-        <v>0.05180280336842857</v>
+        <v>0.03383559462402241</v>
       </c>
       <c r="E9">
-        <v>0.06436524193887294</v>
+        <v>0.05180280320956643</v>
       </c>
       <c r="F9">
-        <v>0.0608850685120671</v>
+        <v>0.06436524162413537</v>
       </c>
       <c r="G9">
-        <v>0.091444429538038</v>
+        <v>0.06088506859816556</v>
       </c>
       <c r="H9">
-        <v>0.09499096651603656</v>
+        <v>0.09144442938459418</v>
       </c>
       <c r="I9">
-        <v>0.1104306162615259</v>
+        <v>0.09499096625075998</v>
       </c>
       <c r="J9">
-        <v>0.1365282890656305</v>
+        <v>0.1104306153129962</v>
       </c>
       <c r="K9">
-        <v>0.1582164133677532</v>
+        <v>0.136528288343998</v>
       </c>
       <c r="L9">
-        <v>0.1634779596313589</v>
+        <v>0.1582164126250322</v>
       </c>
       <c r="M9">
-        <v>0.1810140247855561</v>
+        <v>0.1634779708487942</v>
       </c>
       <c r="N9">
-        <v>0.215897555556153</v>
+        <v>0.1810140412954061</v>
       </c>
       <c r="O9">
-        <v>0.2407205966048332</v>
+        <v>0.2158975774501897</v>
       </c>
       <c r="P9">
-        <v>0.2631507060664566</v>
+        <v>0.2407206268861872</v>
+      </c>
+      <c r="Q9">
+        <v>0.2631507427561269</v>
       </c>
     </row>
     <row r="10">
@@ -859,49 +888,52 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.02037917607847517</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.03208607395179675</v>
+        <v>0.02037917608703133</v>
       </c>
       <c r="D10">
-        <v>0.05055635400633218</v>
+        <v>0.0320860739506228</v>
       </c>
       <c r="E10">
-        <v>0.06307028861378439</v>
+        <v>0.05055635383056434</v>
       </c>
       <c r="F10">
-        <v>0.06190235548748035</v>
+        <v>0.06307028831578687</v>
       </c>
       <c r="G10">
-        <v>0.09229130815535824</v>
+        <v>0.06190235549580869</v>
       </c>
       <c r="H10">
-        <v>0.0948080009998995</v>
+        <v>0.0922913079113632</v>
       </c>
       <c r="I10">
-        <v>0.108960881250343</v>
+        <v>0.09480800066900952</v>
       </c>
       <c r="J10">
-        <v>0.1324312972389058</v>
+        <v>0.1089608803679676</v>
       </c>
       <c r="K10">
-        <v>0.1522127924034269</v>
+        <v>0.1324312957176089</v>
       </c>
       <c r="L10">
-        <v>0.1566748533909316</v>
+        <v>0.1522127924612822</v>
       </c>
       <c r="M10">
-        <v>0.1727336947539083</v>
+        <v>0.1566748629167884</v>
       </c>
       <c r="N10">
-        <v>0.2083218813489481</v>
+        <v>0.1727337163595469</v>
       </c>
       <c r="O10">
-        <v>0.2361785388726247</v>
+        <v>0.2083219089592222</v>
       </c>
       <c r="P10">
-        <v>0.2649315215093484</v>
+        <v>0.2361785661129545</v>
+      </c>
+      <c r="Q10">
+        <v>0.2649315621095958</v>
       </c>
     </row>
     <row r="11">
@@ -911,49 +943,52 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.02083835388968475</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.02984116531261205</v>
+        <v>0.02083835389815836</v>
       </c>
       <c r="D11">
-        <v>0.04804882615383654</v>
+        <v>0.02984116531275938</v>
       </c>
       <c r="E11">
-        <v>0.06215283469566935</v>
+        <v>0.04804882599533267</v>
       </c>
       <c r="F11">
-        <v>0.06026820963395052</v>
+        <v>0.06215283440420216</v>
       </c>
       <c r="G11">
-        <v>0.09011303876099008</v>
+        <v>0.0602682096602023</v>
       </c>
       <c r="H11">
-        <v>0.09488276036053978</v>
+        <v>0.09011303881400856</v>
       </c>
       <c r="I11">
-        <v>0.1097223769017921</v>
+        <v>0.09488276072216517</v>
       </c>
       <c r="J11">
-        <v>0.133899795820557</v>
+        <v>0.1097223767927622</v>
       </c>
       <c r="K11">
-        <v>0.1457411098415865</v>
+        <v>0.1338997965951989</v>
       </c>
       <c r="L11">
-        <v>0.1494116722309554</v>
+        <v>0.1457411119388239</v>
       </c>
       <c r="M11">
-        <v>0.1624463007614336</v>
+        <v>0.1494116806926162</v>
       </c>
       <c r="N11">
-        <v>0.1959573890837714</v>
+        <v>0.1624463205094047</v>
       </c>
       <c r="O11">
-        <v>0.225166078595058</v>
+        <v>0.195957415379282</v>
       </c>
       <c r="P11">
-        <v>0.2428368903794165</v>
+        <v>0.225166109409749</v>
+      </c>
+      <c r="Q11">
+        <v>0.2428369250117782</v>
       </c>
     </row>
     <row r="12">
@@ -963,49 +998,52 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.02056848975755066</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.04789589014749251</v>
+        <v>0.02056848968032332</v>
       </c>
       <c r="D12">
-        <v>0.05898843778477691</v>
+        <v>0.04789588966918124</v>
       </c>
       <c r="E12">
-        <v>0.09102421864911747</v>
+        <v>0.05898843708385204</v>
       </c>
       <c r="F12">
-        <v>0.1100651095689416</v>
+        <v>0.09102421768162028</v>
       </c>
       <c r="G12">
-        <v>0.1210638513315895</v>
+        <v>0.1100651084275988</v>
       </c>
       <c r="H12">
-        <v>0.1513570298021881</v>
+        <v>0.1210638492783168</v>
       </c>
       <c r="I12">
-        <v>0.204456019950376</v>
+        <v>0.151357026873727</v>
       </c>
       <c r="J12">
-        <v>0.2848092959940216</v>
+        <v>0.2044560143254825</v>
       </c>
       <c r="K12">
-        <v>0.3609318238269962</v>
+        <v>0.2848092932996738</v>
       </c>
       <c r="L12">
-        <v>0.4549337091802102</v>
+        <v>0.3609318278997265</v>
       </c>
       <c r="M12">
-        <v>0.494963341056022</v>
+        <v>0.4549337087544991</v>
       </c>
       <c r="N12">
-        <v>0.5003429505213456</v>
+        <v>0.4949633364262328</v>
       </c>
       <c r="O12">
-        <v>0.5053844275823094</v>
+        <v>0.5003429456395745</v>
       </c>
       <c r="P12">
-        <v>0.5403970374579325</v>
+        <v>0.5053844288139826</v>
+      </c>
+      <c r="Q12">
+        <v>0.5403970510633734</v>
       </c>
     </row>
     <row r="13">
@@ -1015,49 +1053,52 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.02182457012504513</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.07407771192074064</v>
+        <v>0.02182457013474637</v>
       </c>
       <c r="D13">
-        <v>0.09419335950455565</v>
+        <v>0.07407771158899057</v>
       </c>
       <c r="E13">
-        <v>0.104495326929208</v>
+        <v>0.09419335896193148</v>
       </c>
       <c r="F13">
-        <v>0.156612057030279</v>
+        <v>0.1044953282756528</v>
       </c>
       <c r="G13">
-        <v>0.2008718298621476</v>
+        <v>0.1566120593099551</v>
       </c>
       <c r="H13">
-        <v>0.2154651702427262</v>
+        <v>0.2008718248522671</v>
       </c>
       <c r="I13">
-        <v>0.244037026746233</v>
+        <v>0.2154651645237252</v>
       </c>
       <c r="J13">
-        <v>0.3358196897659236</v>
+        <v>0.244037024346302</v>
       </c>
       <c r="K13">
-        <v>0.4198825948587486</v>
+        <v>0.3358196744186964</v>
       </c>
       <c r="L13">
-        <v>0.452559906544265</v>
+        <v>0.4198825952850221</v>
       </c>
       <c r="M13">
-        <v>0.4629984427426453</v>
+        <v>0.4525599124180735</v>
       </c>
       <c r="N13">
-        <v>0.4935003746019808</v>
+        <v>0.4629984510374577</v>
       </c>
       <c r="O13">
-        <v>0.5076053403371614</v>
+        <v>0.4935003880839371</v>
       </c>
       <c r="P13">
-        <v>0.5486725153140166</v>
+        <v>0.507605341083805</v>
+      </c>
+      <c r="Q13">
+        <v>0.5486724976082098</v>
       </c>
     </row>
     <row r="14">
@@ -1067,49 +1108,52 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.02255313958519811</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.0331192089370852</v>
+        <v>0.02255313957224614</v>
       </c>
       <c r="D14">
-        <v>0.04972202596117192</v>
+        <v>0.03311920895790788</v>
       </c>
       <c r="E14">
-        <v>0.05156720060674236</v>
+        <v>0.04972202576751628</v>
       </c>
       <c r="F14">
-        <v>0.07566463767094767</v>
+        <v>0.05156720046256025</v>
       </c>
       <c r="G14">
-        <v>0.06745675837010867</v>
+        <v>0.07566463731775341</v>
       </c>
       <c r="H14">
-        <v>0.09260372333621958</v>
+        <v>0.0674567582905603</v>
       </c>
       <c r="I14">
-        <v>0.1031539849810476</v>
+        <v>0.09260372352583857</v>
       </c>
       <c r="J14">
-        <v>0.119177021140319</v>
+        <v>0.1031539861954395</v>
       </c>
       <c r="K14">
-        <v>0.1404969045687094</v>
+        <v>0.1191770224520053</v>
       </c>
       <c r="L14">
-        <v>0.1517606197033634</v>
+        <v>0.1404969075469948</v>
       </c>
       <c r="M14">
-        <v>0.1807116031639849</v>
+        <v>0.1517606090815313</v>
       </c>
       <c r="N14">
-        <v>0.2137723142366406</v>
+        <v>0.1807118021182937</v>
       </c>
       <c r="O14">
-        <v>0.2563792967770936</v>
+        <v>0.2137723558127442</v>
       </c>
       <c r="P14">
-        <v>0.3109788051327859</v>
+        <v>0.2563793360937074</v>
+      </c>
+      <c r="Q14">
+        <v>0.3109788384017212</v>
       </c>
     </row>
     <row r="15">
@@ -1119,49 +1163,52 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.02192941115942398</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.03131438277385445</v>
+        <v>0.02192941114923586</v>
       </c>
       <c r="D15">
-        <v>0.04811687616414573</v>
+        <v>0.03131438279691223</v>
       </c>
       <c r="E15">
-        <v>0.05147181128014533</v>
+        <v>0.04811687594061531</v>
       </c>
       <c r="F15">
-        <v>0.07485352710985615</v>
+        <v>0.05147181110503685</v>
       </c>
       <c r="G15">
-        <v>0.07272118478992273</v>
+        <v>0.07485352677611579</v>
       </c>
       <c r="H15">
-        <v>0.09188877240111304</v>
+        <v>0.07272118472467071</v>
       </c>
       <c r="I15">
-        <v>0.1006453754174371</v>
+        <v>0.0918887726507821</v>
       </c>
       <c r="J15">
-        <v>0.1096139354383322</v>
+        <v>0.1006453766488988</v>
       </c>
       <c r="K15">
-        <v>0.1316852792500491</v>
+        <v>0.1096139366466745</v>
       </c>
       <c r="L15">
-        <v>0.1425976119373111</v>
+        <v>0.1316852798166744</v>
       </c>
       <c r="M15">
-        <v>0.1690894413678199</v>
+        <v>0.1425976136753984</v>
       </c>
       <c r="N15">
-        <v>0.2088134125904483</v>
+        <v>0.1690894513823863</v>
       </c>
       <c r="O15">
-        <v>0.2353644143015134</v>
+        <v>0.2088134371839616</v>
       </c>
       <c r="P15">
-        <v>0.2524579857081722</v>
+        <v>0.235364449150548</v>
+      </c>
+      <c r="Q15">
+        <v>0.2524580243771157</v>
       </c>
     </row>
     <row r="16">
@@ -1171,49 +1218,52 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.02016030016084502</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.03068303748520373</v>
+        <v>0.02016030013659176</v>
       </c>
       <c r="D16">
-        <v>0.04585069522164931</v>
+        <v>0.0306830375068331</v>
       </c>
       <c r="E16">
-        <v>0.04864491299533069</v>
+        <v>0.04585069503128003</v>
       </c>
       <c r="F16">
-        <v>0.07257912795549115</v>
+        <v>0.04864491284243466</v>
       </c>
       <c r="G16">
-        <v>0.06628071765272781</v>
+        <v>0.07257912767629293</v>
       </c>
       <c r="H16">
-        <v>0.08937479127769021</v>
+        <v>0.06628071765544508</v>
       </c>
       <c r="I16">
-        <v>0.09993433813851205</v>
+        <v>0.08937479167234286</v>
       </c>
       <c r="J16">
-        <v>0.1136779902745433</v>
+        <v>0.09993433970433496</v>
       </c>
       <c r="K16">
-        <v>0.1330572413232672</v>
+        <v>0.1136779922830212</v>
       </c>
       <c r="L16">
-        <v>0.1425333464844549</v>
+        <v>0.1330572436482523</v>
       </c>
       <c r="M16">
-        <v>0.178918570816934</v>
+        <v>0.1425333311630412</v>
       </c>
       <c r="N16">
-        <v>0.2247282141419613</v>
+        <v>0.1789186896166562</v>
       </c>
       <c r="O16">
-        <v>0.2598250187401329</v>
+        <v>0.2247283125777659</v>
       </c>
       <c r="P16">
-        <v>0.2736611961256227</v>
+        <v>0.2598250594930066</v>
+      </c>
+      <c r="Q16">
+        <v>0.273661243891679</v>
       </c>
     </row>
     <row r="17">
@@ -1223,49 +1273,52 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.02297430417299418</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.03202498055010849</v>
+        <v>0.02297430415335822</v>
       </c>
       <c r="D17">
-        <v>0.04766979366533508</v>
+        <v>0.03202498057674097</v>
       </c>
       <c r="E17">
-        <v>0.05022177535272598</v>
+        <v>0.04766979345972477</v>
       </c>
       <c r="F17">
-        <v>0.0740774744103242</v>
+        <v>0.05022177520469351</v>
       </c>
       <c r="G17">
-        <v>0.06959321188919554</v>
+        <v>0.07407747412573407</v>
       </c>
       <c r="H17">
-        <v>0.08771042217845504</v>
+        <v>0.06959321173238953</v>
       </c>
       <c r="I17">
-        <v>0.0975378296516124</v>
+        <v>0.08771042243669547</v>
       </c>
       <c r="J17">
-        <v>0.1101749988910397</v>
+        <v>0.097537830761391</v>
       </c>
       <c r="K17">
-        <v>0.1280482338883004</v>
+        <v>0.1101750002959065</v>
       </c>
       <c r="L17">
-        <v>0.1357271209841751</v>
+        <v>0.128048235937529</v>
       </c>
       <c r="M17">
-        <v>0.1709245433309673</v>
+        <v>0.1357271249109964</v>
       </c>
       <c r="N17">
-        <v>0.2103275009230217</v>
+        <v>0.1709245556436813</v>
       </c>
       <c r="O17">
-        <v>0.2482967768958136</v>
+        <v>0.210327533226733</v>
       </c>
       <c r="P17">
-        <v>0.25783246017304</v>
+        <v>0.248296826739427</v>
+      </c>
+      <c r="Q17">
+        <v>0.2578325078331697</v>
       </c>
     </row>
     <row r="18">
@@ -1275,49 +1328,52 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.02061033297029846</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.04838069771069375</v>
+        <v>0.02061033290793723</v>
       </c>
       <c r="D18">
-        <v>0.06289352108418989</v>
+        <v>0.04838069732849681</v>
       </c>
       <c r="E18">
-        <v>0.1000352955361322</v>
+        <v>0.06289352059543341</v>
       </c>
       <c r="F18">
-        <v>0.1104755968941481</v>
+        <v>0.1000352948730184</v>
       </c>
       <c r="G18">
-        <v>0.137771135485897</v>
+        <v>0.1104755962733932</v>
       </c>
       <c r="H18">
-        <v>0.1558326805377068</v>
+        <v>0.1377711339034242</v>
       </c>
       <c r="I18">
-        <v>0.204968800525888</v>
+        <v>0.155832677589352</v>
       </c>
       <c r="J18">
-        <v>0.2765996305422713</v>
+        <v>0.204968797135197</v>
       </c>
       <c r="K18">
-        <v>0.3536974930540484</v>
+        <v>0.2765996260546298</v>
       </c>
       <c r="L18">
-        <v>0.4301135900653281</v>
+        <v>0.3536974981245485</v>
       </c>
       <c r="M18">
-        <v>0.4733793605474895</v>
+        <v>0.4301135950736166</v>
       </c>
       <c r="N18">
-        <v>0.4866426106750049</v>
+        <v>0.4733793640200387</v>
       </c>
       <c r="O18">
-        <v>0.4946789746543391</v>
+        <v>0.486642606257591</v>
       </c>
       <c r="P18">
-        <v>0.5030462441178406</v>
+        <v>0.4946789687104958</v>
+      </c>
+      <c r="Q18">
+        <v>0.5030462310637229</v>
       </c>
     </row>
     <row r="19">
@@ -1327,49 +1383,52 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.01896591443076634</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.0444080427613599</v>
+        <v>0.01896591438117212</v>
       </c>
       <c r="D19">
-        <v>0.05481907890241167</v>
+        <v>0.04440804256854758</v>
       </c>
       <c r="E19">
-        <v>0.08470993830247853</v>
+        <v>0.05481907843474931</v>
       </c>
       <c r="F19">
-        <v>0.0837181932538742</v>
+        <v>0.084709937670988</v>
       </c>
       <c r="G19">
-        <v>0.1239780556787815</v>
+        <v>0.08371819239812861</v>
       </c>
       <c r="H19">
-        <v>0.1288929007769558</v>
+        <v>0.1239780552248289</v>
       </c>
       <c r="I19">
-        <v>0.1702752599258546</v>
+        <v>0.1288929004034413</v>
       </c>
       <c r="J19">
-        <v>0.2139907667142472</v>
+        <v>0.1702752595218679</v>
       </c>
       <c r="K19">
-        <v>0.266024844457811</v>
+        <v>0.2139907697743703</v>
       </c>
       <c r="L19">
-        <v>0.3171453219915139</v>
+        <v>0.266024858192539</v>
       </c>
       <c r="M19">
-        <v>0.3532540274166102</v>
+        <v>0.3171453393232198</v>
       </c>
       <c r="N19">
-        <v>0.3974067218736814</v>
+        <v>0.3532540424182466</v>
       </c>
       <c r="O19">
-        <v>0.4213620981654234</v>
+        <v>0.3974067336138576</v>
       </c>
       <c r="P19">
-        <v>0.4563017956820684</v>
+        <v>0.4213621027836526</v>
+      </c>
+      <c r="Q19">
+        <v>0.4563017795873035</v>
       </c>
     </row>
     <row r="20">
@@ -1379,49 +1438,52 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.01833321149596756</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.03421185367376478</v>
+        <v>0.01833321147850608</v>
       </c>
       <c r="D20">
-        <v>0.05264119975118964</v>
+        <v>0.03421185374518998</v>
       </c>
       <c r="E20">
-        <v>0.08168591003679504</v>
+        <v>0.05264119946414825</v>
       </c>
       <c r="F20">
-        <v>0.07720906881935463</v>
+        <v>0.08168590940410037</v>
       </c>
       <c r="G20">
-        <v>0.08650603073942376</v>
+        <v>0.07720906858411913</v>
       </c>
       <c r="H20">
-        <v>0.1072937978780646</v>
+        <v>0.08650603014983493</v>
       </c>
       <c r="I20">
-        <v>0.1544287518050668</v>
+        <v>0.1072937951437237</v>
       </c>
       <c r="J20">
-        <v>0.1859015557082121</v>
+        <v>0.1544287540640634</v>
       </c>
       <c r="K20">
-        <v>0.2107175076185852</v>
+        <v>0.1859015679420272</v>
       </c>
       <c r="L20">
-        <v>0.2511346142321396</v>
+        <v>0.2107175218458647</v>
       </c>
       <c r="M20">
-        <v>0.2844170226813624</v>
+        <v>0.2511346392483647</v>
       </c>
       <c r="N20">
-        <v>0.2970422422254757</v>
+        <v>0.2844170532413647</v>
       </c>
       <c r="O20">
-        <v>0.3324540915964564</v>
+        <v>0.2970422676622574</v>
       </c>
       <c r="P20">
-        <v>0.3686372932553561</v>
+        <v>0.3324541016726026</v>
+      </c>
+      <c r="Q20">
+        <v>0.368637273565163</v>
       </c>
     </row>
     <row r="21">
@@ -1431,49 +1493,52 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.04040732143795567</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.03918778581483084</v>
+        <v>0.04040732114213708</v>
       </c>
       <c r="D21">
-        <v>0.07004542667696734</v>
+        <v>0.03918778527947442</v>
       </c>
       <c r="E21">
-        <v>0.1658267680327372</v>
+        <v>0.07004542640782141</v>
       </c>
       <c r="F21">
-        <v>0.1433556169344894</v>
+        <v>0.1658267614726232</v>
       </c>
       <c r="G21">
-        <v>0.1721702243775829</v>
+        <v>0.1433556169270249</v>
       </c>
       <c r="H21">
-        <v>0.2544230998112293</v>
+        <v>0.1721702247925051</v>
       </c>
       <c r="I21">
-        <v>0.3473920332117321</v>
+        <v>0.2544230949924878</v>
       </c>
       <c r="J21">
-        <v>0.3858837838486736</v>
+        <v>0.3473920346278639</v>
       </c>
       <c r="K21">
-        <v>0.4433842252542836</v>
+        <v>0.3858837963398356</v>
       </c>
       <c r="L21">
-        <v>0.4769629171257458</v>
+        <v>0.443384246550139</v>
       </c>
       <c r="M21">
-        <v>0.5000165366430188</v>
+        <v>0.476962922677345</v>
       </c>
       <c r="N21">
-        <v>0.5222823644039596</v>
+        <v>0.5000165016867245</v>
       </c>
       <c r="O21">
-        <v>0.5245488323276553</v>
+        <v>0.5222822994748992</v>
       </c>
       <c r="P21">
-        <v>0.5515231039741333</v>
+        <v>0.5245487732240468</v>
+      </c>
+      <c r="Q21">
+        <v>0.5515230596935822</v>
       </c>
     </row>
     <row r="22">
@@ -1483,49 +1548,52 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.04000148219643362</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.03813730969907536</v>
+        <v>0.04000148185041763</v>
       </c>
       <c r="D22">
-        <v>0.06614740163041921</v>
+        <v>0.03813730914824853</v>
       </c>
       <c r="E22">
-        <v>0.1709170096826577</v>
+        <v>0.06614740132093999</v>
       </c>
       <c r="F22">
-        <v>0.1431518405122929</v>
+        <v>0.1709170025945487</v>
       </c>
       <c r="G22">
-        <v>0.1550200404432004</v>
+        <v>0.1431518404911891</v>
       </c>
       <c r="H22">
-        <v>0.2485551353500431</v>
+        <v>0.1550200480805183</v>
       </c>
       <c r="I22">
-        <v>0.3215439743310384</v>
+        <v>0.2485551336771351</v>
       </c>
       <c r="J22">
-        <v>0.3794732629016327</v>
+        <v>0.3215439678197864</v>
       </c>
       <c r="K22">
-        <v>0.4200847220036049</v>
+        <v>0.3794732546119628</v>
       </c>
       <c r="L22">
-        <v>0.4705187177665652</v>
+        <v>0.42008470382878</v>
       </c>
       <c r="M22">
-        <v>0.502702528709662</v>
+        <v>0.4705186748273929</v>
       </c>
       <c r="N22">
-        <v>0.5084085033224242</v>
+        <v>0.5027023952064487</v>
       </c>
       <c r="O22">
-        <v>0.5138628310917641</v>
+        <v>0.5084083214379058</v>
       </c>
       <c r="P22">
-        <v>0.5547377942851467</v>
+        <v>0.513862622226785</v>
+      </c>
+      <c r="Q22">
+        <v>0.5547375690123042</v>
       </c>
     </row>
     <row r="23">
@@ -1535,49 +1603,52 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.02169893790471511</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.03437559378906285</v>
+        <v>0.02169893779484378</v>
       </c>
       <c r="D23">
-        <v>0.09175874955386254</v>
+        <v>0.03437559357676212</v>
       </c>
       <c r="E23">
-        <v>0.07286985222596021</v>
+        <v>0.09175875067404671</v>
       </c>
       <c r="F23">
-        <v>0.1610552069770838</v>
+        <v>0.07286985533695334</v>
       </c>
       <c r="G23">
-        <v>0.2554268221414772</v>
+        <v>0.1610552555655441</v>
       </c>
       <c r="H23">
-        <v>0.3437947090777287</v>
+        <v>0.2554268168391027</v>
       </c>
       <c r="I23">
-        <v>0.3823595178038112</v>
+        <v>0.3437947161035048</v>
       </c>
       <c r="J23">
-        <v>0.3913777395006391</v>
+        <v>0.3823595447798493</v>
       </c>
       <c r="K23">
-        <v>0.461043319187003</v>
+        <v>0.3913777645156048</v>
       </c>
       <c r="L23">
-        <v>0.5109861944474743</v>
+        <v>0.4610433408027758</v>
       </c>
       <c r="M23">
-        <v>0.5511968766833051</v>
+        <v>0.5109863221693955</v>
       </c>
       <c r="N23">
-        <v>0.5902978255447546</v>
+        <v>0.5511971531489497</v>
       </c>
       <c r="O23">
-        <v>0.6109091088500476</v>
+        <v>0.5902982609970457</v>
       </c>
       <c r="P23">
-        <v>0.654229313496853</v>
+        <v>0.6109096353617698</v>
+      </c>
+      <c r="Q23">
+        <v>0.6542300197318049</v>
       </c>
     </row>
     <row r="24">
@@ -1587,49 +1658,52 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.02080513651430926</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.03210257210312972</v>
+        <v>0.02080513649712978</v>
       </c>
       <c r="D24">
-        <v>0.07692472195543198</v>
+        <v>0.0321025721237862</v>
       </c>
       <c r="E24">
-        <v>0.06383258868358588</v>
+        <v>0.07692472134721717</v>
       </c>
       <c r="F24">
-        <v>0.0783825803466689</v>
+        <v>0.06383258867898078</v>
       </c>
       <c r="G24">
-        <v>0.09084576223740126</v>
+        <v>0.07838257951119432</v>
       </c>
       <c r="H24">
-        <v>0.1135170750571886</v>
+        <v>0.09084576179690129</v>
       </c>
       <c r="I24">
-        <v>0.1915749228285009</v>
+        <v>0.1135170749337991</v>
       </c>
       <c r="J24">
-        <v>0.2185962245363803</v>
+        <v>0.1915749372044327</v>
       </c>
       <c r="K24">
-        <v>0.2529072611119899</v>
+        <v>0.2185962341816918</v>
       </c>
       <c r="L24">
-        <v>0.3010809697139009</v>
+        <v>0.2529072636077478</v>
       </c>
       <c r="M24">
-        <v>0.3827523267373741</v>
+        <v>0.3010809558048003</v>
       </c>
       <c r="N24">
-        <v>0.424940660479125</v>
+        <v>0.3827522737340809</v>
       </c>
       <c r="O24">
-        <v>0.5007781397558642</v>
+        <v>0.4249405794199385</v>
       </c>
       <c r="P24">
-        <v>0.5765833447584525</v>
+        <v>0.5007779906258765</v>
+      </c>
+      <c r="Q24">
+        <v>0.5765831851633459</v>
       </c>
     </row>
     <row r="25">
@@ -1639,49 +1713,52 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.02083344619995531</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.03195066923455803</v>
+        <v>0.02083344619138927</v>
       </c>
       <c r="D25">
-        <v>0.08019255776298484</v>
+        <v>0.03195066925189161</v>
       </c>
       <c r="E25">
-        <v>0.06740044118986155</v>
+        <v>0.08019255724994212</v>
       </c>
       <c r="F25">
-        <v>0.08671226208301408</v>
+        <v>0.06740044100320808</v>
       </c>
       <c r="G25">
-        <v>0.1269722416151087</v>
+        <v>0.08671226161916634</v>
       </c>
       <c r="H25">
-        <v>0.1634773211167532</v>
+        <v>0.1269722416959281</v>
       </c>
       <c r="I25">
-        <v>0.2169657481061548</v>
+        <v>0.1634773224804091</v>
       </c>
       <c r="J25">
-        <v>0.2254582386815287</v>
+        <v>0.2169657602994244</v>
       </c>
       <c r="K25">
-        <v>0.2468971610082572</v>
+        <v>0.2254582440373835</v>
       </c>
       <c r="L25">
-        <v>0.2838132946787288</v>
+        <v>0.2468971655913733</v>
       </c>
       <c r="M25">
-        <v>0.3417004792980098</v>
+        <v>0.2838132891719999</v>
       </c>
       <c r="N25">
-        <v>0.408479856843477</v>
+        <v>0.3417004293366844</v>
       </c>
       <c r="O25">
-        <v>0.4525326349547039</v>
+        <v>0.4084797713887771</v>
       </c>
       <c r="P25">
-        <v>0.5340167974613066</v>
+        <v>0.4525325182035952</v>
+      </c>
+      <c r="Q25">
+        <v>0.5340166165937942</v>
       </c>
     </row>
     <row r="26">
@@ -1691,49 +1768,52 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.01826124303187071</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.03148571191663452</v>
+        <v>0.01826124301174326</v>
       </c>
       <c r="D26">
-        <v>0.0757530795657847</v>
+        <v>0.03148571187239979</v>
       </c>
       <c r="E26">
-        <v>0.06991091496695645</v>
+        <v>0.07575307930139641</v>
       </c>
       <c r="F26">
-        <v>0.08401243187345697</v>
+        <v>0.0699109147803737</v>
       </c>
       <c r="G26">
-        <v>0.09113752246275941</v>
+        <v>0.08401243133845859</v>
       </c>
       <c r="H26">
-        <v>0.1295407791723787</v>
+        <v>0.09113752244738804</v>
       </c>
       <c r="I26">
-        <v>0.1979949189002602</v>
+        <v>0.1295407808828596</v>
       </c>
       <c r="J26">
-        <v>0.2414281012369004</v>
+        <v>0.1979949286388881</v>
       </c>
       <c r="K26">
-        <v>0.2761699201612401</v>
+        <v>0.2414281139019563</v>
       </c>
       <c r="L26">
-        <v>0.3434030582589949</v>
+        <v>0.2761699164643763</v>
       </c>
       <c r="M26">
-        <v>0.4016028213029392</v>
+        <v>0.3434030225445475</v>
       </c>
       <c r="N26">
-        <v>0.4747555961070611</v>
+        <v>0.4016027576049354</v>
       </c>
       <c r="O26">
-        <v>0.5440375230114866</v>
+        <v>0.474755498183862</v>
       </c>
       <c r="P26">
-        <v>0.6610970964827654</v>
+        <v>0.5440373798620726</v>
+      </c>
+      <c r="Q26">
+        <v>0.6610969224773967</v>
       </c>
     </row>
     <row r="27">
@@ -1743,49 +1823,52 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.01819544630677883</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>0.0319145166402296</v>
+        <v>0.01819544628513647</v>
       </c>
       <c r="D27">
-        <v>0.07395011768255144</v>
+        <v>0.03191451660170375</v>
       </c>
       <c r="E27">
-        <v>0.06813004429859137</v>
+        <v>0.07395011744243007</v>
       </c>
       <c r="F27">
-        <v>0.0779721628986062</v>
+        <v>0.06813004410113055</v>
       </c>
       <c r="G27">
-        <v>0.08154918091369145</v>
+        <v>0.07797216239467586</v>
       </c>
       <c r="H27">
-        <v>0.09640847634327732</v>
+        <v>0.08154918074291229</v>
       </c>
       <c r="I27">
-        <v>0.1256245987324932</v>
+        <v>0.09640847572146605</v>
       </c>
       <c r="J27">
-        <v>0.1370669917337376</v>
+        <v>0.1256245968336438</v>
       </c>
       <c r="K27">
-        <v>0.14481624546686</v>
+        <v>0.1370669975049935</v>
       </c>
       <c r="L27">
-        <v>0.1572331871205016</v>
+        <v>0.1448162476261492</v>
       </c>
       <c r="M27">
-        <v>0.1883800660549068</v>
+        <v>0.1572331872332787</v>
       </c>
       <c r="N27">
-        <v>0.2322955904624474</v>
+        <v>0.1883800769475319</v>
       </c>
       <c r="O27">
-        <v>0.2424733485024071</v>
+        <v>0.2322955955636617</v>
       </c>
       <c r="P27">
-        <v>0.3336604242063849</v>
+        <v>0.2424733301115941</v>
+      </c>
+      <c r="Q27">
+        <v>0.3336604098898112</v>
       </c>
     </row>
     <row r="28">
@@ -1795,49 +1878,52 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.02002311882721797</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.03130131163788685</v>
+        <v>0.02002311881691898</v>
       </c>
       <c r="D28">
-        <v>0.08014158857966391</v>
+        <v>0.03130131165672878</v>
       </c>
       <c r="E28">
-        <v>0.06642886644168322</v>
+        <v>0.08014158802834059</v>
       </c>
       <c r="F28">
-        <v>0.08507578797484405</v>
+        <v>0.06642886635354639</v>
       </c>
       <c r="G28">
-        <v>0.1120043314193457</v>
+        <v>0.08507578723469555</v>
       </c>
       <c r="H28">
-        <v>0.1354678612828211</v>
+        <v>0.1120043294617212</v>
       </c>
       <c r="I28">
-        <v>0.146981022300585</v>
+        <v>0.1354678603662208</v>
       </c>
       <c r="J28">
-        <v>0.1510436669968899</v>
+        <v>0.1469810265431415</v>
       </c>
       <c r="K28">
-        <v>0.1490772947534608</v>
+        <v>0.1510436677036365</v>
       </c>
       <c r="L28">
-        <v>0.1623862038030535</v>
+        <v>0.1490772950186492</v>
       </c>
       <c r="M28">
-        <v>0.1868104828592568</v>
+        <v>0.1623862053639298</v>
       </c>
       <c r="N28">
-        <v>0.2275105950379777</v>
+        <v>0.1868104824927083</v>
       </c>
       <c r="O28">
-        <v>0.2399526407954831</v>
+        <v>0.2275105963509453</v>
       </c>
       <c r="P28">
-        <v>0.2941237929530945</v>
+        <v>0.2399526448793805</v>
+      </c>
+      <c r="Q28">
+        <v>0.2941237576991255</v>
       </c>
     </row>
     <row r="29">
@@ -1847,49 +1933,52 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.02112941444881189</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.03183376639031521</v>
+        <v>0.02112941443240368</v>
       </c>
       <c r="D29">
-        <v>0.07989227502804364</v>
+        <v>0.03183376640875635</v>
       </c>
       <c r="E29">
-        <v>0.06776342531252877</v>
+        <v>0.07989227442375557</v>
       </c>
       <c r="F29">
-        <v>0.08501943447487159</v>
+        <v>0.0677634251068947</v>
       </c>
       <c r="G29">
-        <v>0.1106069020435079</v>
+        <v>0.0850194334607699</v>
       </c>
       <c r="H29">
-        <v>0.1328123516120623</v>
+        <v>0.1106069003934675</v>
       </c>
       <c r="I29">
-        <v>0.1477660310461653</v>
+        <v>0.1328123492626179</v>
       </c>
       <c r="J29">
-        <v>0.1531498676232198</v>
+        <v>0.1477660331384926</v>
       </c>
       <c r="K29">
-        <v>0.1512838093392486</v>
+        <v>0.1531498667552972</v>
       </c>
       <c r="L29">
-        <v>0.1614911255878907</v>
+        <v>0.1512838100580228</v>
       </c>
       <c r="M29">
-        <v>0.1797235705850851</v>
+        <v>0.1614911243408103</v>
       </c>
       <c r="N29">
-        <v>0.2155729244937057</v>
+        <v>0.1797235639950436</v>
       </c>
       <c r="O29">
-        <v>0.2225671730937245</v>
+        <v>0.2155729224855436</v>
       </c>
       <c r="P29">
-        <v>0.2732943009749813</v>
+        <v>0.222567170273362</v>
+      </c>
+      <c r="Q29">
+        <v>0.2732942665626334</v>
       </c>
     </row>
     <row r="30">
@@ -1899,49 +1988,52 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.02062377334168819</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.03149190212070707</v>
+        <v>0.02062377333253773</v>
       </c>
       <c r="D30">
-        <v>0.07771390155953295</v>
+        <v>0.0314919021470258</v>
       </c>
       <c r="E30">
-        <v>0.06295470654199264</v>
+        <v>0.07771390107549592</v>
       </c>
       <c r="F30">
-        <v>0.08008851365364589</v>
+        <v>0.06295470641184231</v>
       </c>
       <c r="G30">
-        <v>0.1039144611837954</v>
+        <v>0.08008851288907648</v>
       </c>
       <c r="H30">
-        <v>0.1233276264963161</v>
+        <v>0.1039144596903352</v>
       </c>
       <c r="I30">
-        <v>0.1336756894150068</v>
+        <v>0.123327625420544</v>
       </c>
       <c r="J30">
-        <v>0.1387707425351256</v>
+        <v>0.1336756942114605</v>
       </c>
       <c r="K30">
-        <v>0.142918266321433</v>
+        <v>0.1387707409389062</v>
       </c>
       <c r="L30">
-        <v>0.1515275387152385</v>
+        <v>0.142918267310262</v>
       </c>
       <c r="M30">
-        <v>0.1667373019942068</v>
+        <v>0.1515275445527707</v>
       </c>
       <c r="N30">
-        <v>0.1996700167760945</v>
+        <v>0.166737299804616</v>
       </c>
       <c r="O30">
-        <v>0.2078055832627342</v>
+        <v>0.1996700227365987</v>
       </c>
       <c r="P30">
-        <v>0.2520471756580309</v>
+        <v>0.2078056257528249</v>
+      </c>
+      <c r="Q30">
+        <v>0.2520471503579115</v>
       </c>
     </row>
     <row r="31">
@@ -1951,49 +2043,52 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.01929823480043202</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.03009710807536214</v>
+        <v>0.01929823479500636</v>
       </c>
       <c r="D31">
-        <v>0.07624570362560479</v>
+        <v>0.03009710810344435</v>
       </c>
       <c r="E31">
-        <v>0.06495516520248967</v>
+        <v>0.07624570307944412</v>
       </c>
       <c r="F31">
-        <v>0.08082239979442984</v>
+        <v>0.06495516510097055</v>
       </c>
       <c r="G31">
-        <v>0.1052948135781711</v>
+        <v>0.08082239920309364</v>
       </c>
       <c r="H31">
-        <v>0.1231943795330984</v>
+        <v>0.1052948114716115</v>
       </c>
       <c r="I31">
-        <v>0.137734285918823</v>
+        <v>0.1231943793209412</v>
       </c>
       <c r="J31">
-        <v>0.1461077883506169</v>
+        <v>0.1377342849780292</v>
       </c>
       <c r="K31">
-        <v>0.1430249468059704</v>
+        <v>0.1461077814850501</v>
       </c>
       <c r="L31">
-        <v>0.1521953103559479</v>
+        <v>0.143024949026582</v>
       </c>
       <c r="M31">
-        <v>0.16495338056376</v>
+        <v>0.1521953138650749</v>
       </c>
       <c r="N31">
-        <v>0.1927719145654072</v>
+        <v>0.1649533805283537</v>
       </c>
       <c r="O31">
-        <v>0.2027076700823992</v>
+        <v>0.1927719144579411</v>
       </c>
       <c r="P31">
-        <v>0.2285606631638551</v>
+        <v>0.2027076691019238</v>
+      </c>
+      <c r="Q31">
+        <v>0.2285606314679749</v>
       </c>
     </row>
     <row r="32">
@@ -2003,49 +2098,52 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.01996753373255833</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.0320689132068277</v>
+        <v>0.01996753372996141</v>
       </c>
       <c r="D32">
-        <v>0.08288888414699824</v>
+        <v>0.03206891324031924</v>
       </c>
       <c r="E32">
-        <v>0.06763637075786511</v>
+        <v>0.08288888360013469</v>
       </c>
       <c r="F32">
-        <v>0.08604726340762792</v>
+        <v>0.06763637073151707</v>
       </c>
       <c r="G32">
-        <v>0.1170032986510133</v>
+        <v>0.08604726227279469</v>
       </c>
       <c r="H32">
-        <v>0.1391184807406507</v>
+        <v>0.1170032989460296</v>
       </c>
       <c r="I32">
-        <v>0.1626943389822947</v>
+        <v>0.1391184807097618</v>
       </c>
       <c r="J32">
-        <v>0.1640470289799882</v>
+        <v>0.162694344769341</v>
       </c>
       <c r="K32">
-        <v>0.1611779531453827</v>
+        <v>0.1640470315783719</v>
       </c>
       <c r="L32">
-        <v>0.176271082328972</v>
+        <v>0.1611779562191744</v>
       </c>
       <c r="M32">
-        <v>0.2106101213423077</v>
+        <v>0.1762710880726244</v>
       </c>
       <c r="N32">
-        <v>0.2565020750101359</v>
+        <v>0.2106101179670874</v>
       </c>
       <c r="O32">
-        <v>0.2597353653047222</v>
+        <v>0.2565020692858375</v>
       </c>
       <c r="P32">
-        <v>0.3017756517328318</v>
+        <v>0.2597353442817556</v>
+      </c>
+      <c r="Q32">
+        <v>0.3017756126718443</v>
       </c>
     </row>
     <row r="33">
@@ -2055,49 +2153,52 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.01977728053959493</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.03124329670041059</v>
+        <v>0.01977728053179229</v>
       </c>
       <c r="D33">
-        <v>0.07781828958833736</v>
+        <v>0.0312432967140065</v>
       </c>
       <c r="E33">
-        <v>0.06570392310415041</v>
+        <v>0.07781828904263877</v>
       </c>
       <c r="F33">
-        <v>0.08350202673451934</v>
+        <v>0.06570392307952189</v>
       </c>
       <c r="G33">
-        <v>0.1139663443611888</v>
+        <v>0.08350202568582743</v>
       </c>
       <c r="H33">
-        <v>0.1384173060355014</v>
+        <v>0.1139663401538239</v>
       </c>
       <c r="I33">
-        <v>0.1571946156667655</v>
+        <v>0.1384173058874676</v>
       </c>
       <c r="J33">
-        <v>0.1571196176118937</v>
+        <v>0.1571946208268441</v>
       </c>
       <c r="K33">
-        <v>0.1549639597229878</v>
+        <v>0.1571196136946736</v>
       </c>
       <c r="L33">
-        <v>0.1667007130322703</v>
+        <v>0.1549639636374534</v>
       </c>
       <c r="M33">
-        <v>0.1978037448314267</v>
+        <v>0.1667007142178293</v>
       </c>
       <c r="N33">
-        <v>0.2419238591054714</v>
+        <v>0.1978037441174414</v>
       </c>
       <c r="O33">
-        <v>0.2486787408344469</v>
+        <v>0.2419238613931823</v>
       </c>
       <c r="P33">
-        <v>0.2875166593012987</v>
+        <v>0.2486787362173526</v>
+      </c>
+      <c r="Q33">
+        <v>0.2875166193601125</v>
       </c>
     </row>
     <row r="34">
@@ -2107,49 +2208,52 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.02148447267110154</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.03240002974688028</v>
+        <v>0.02148447266577813</v>
       </c>
       <c r="D34">
-        <v>0.08151827991565064</v>
+        <v>0.03240002978252854</v>
       </c>
       <c r="E34">
-        <v>0.06788820287366171</v>
+        <v>0.08151827939203571</v>
       </c>
       <c r="F34">
-        <v>0.08547364258387258</v>
+        <v>0.06788820284511199</v>
       </c>
       <c r="G34">
-        <v>0.1107739685990066</v>
+        <v>0.08547364188209938</v>
       </c>
       <c r="H34">
-        <v>0.1336685967032791</v>
+        <v>0.1107739670445831</v>
       </c>
       <c r="I34">
-        <v>0.1515665731737104</v>
+        <v>0.1336685950847731</v>
       </c>
       <c r="J34">
-        <v>0.1544124078061511</v>
+        <v>0.1515665781386686</v>
       </c>
       <c r="K34">
-        <v>0.1493870134015326</v>
+        <v>0.154412409895883</v>
       </c>
       <c r="L34">
-        <v>0.164299034067115</v>
+        <v>0.1493870160416306</v>
       </c>
       <c r="M34">
-        <v>0.1938730838454632</v>
+        <v>0.1642990360816772</v>
       </c>
       <c r="N34">
-        <v>0.2344255110991078</v>
+        <v>0.1938730863429661</v>
       </c>
       <c r="O34">
-        <v>0.2356449581962731</v>
+        <v>0.2344255103188755</v>
       </c>
       <c r="P34">
-        <v>0.2773761123057999</v>
+        <v>0.2356449497205715</v>
+      </c>
+      <c r="Q34">
+        <v>0.2773760772372198</v>
       </c>
     </row>
     <row r="35">
@@ -2159,49 +2263,52 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.01967464567505151</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.0302832011309454</v>
+        <v>0.01967464567455335</v>
       </c>
       <c r="D35">
-        <v>0.0765432750205306</v>
+        <v>0.03028320116048133</v>
       </c>
       <c r="E35">
-        <v>0.06567539394162103</v>
+        <v>0.07654327453111742</v>
       </c>
       <c r="F35">
-        <v>0.08130097457093255</v>
+        <v>0.06567539393057464</v>
       </c>
       <c r="G35">
-        <v>0.1080415920397886</v>
+        <v>0.08130097331574626</v>
       </c>
       <c r="H35">
-        <v>0.126432013231972</v>
+        <v>0.1080415903019339</v>
       </c>
       <c r="I35">
-        <v>0.1455584864546559</v>
+        <v>0.126432011940445</v>
       </c>
       <c r="J35">
-        <v>0.1534687612444318</v>
+        <v>0.1455584901243463</v>
       </c>
       <c r="K35">
-        <v>0.1494055894911734</v>
+        <v>0.1534687621061994</v>
       </c>
       <c r="L35">
-        <v>0.1591320001023731</v>
+        <v>0.1494055893706637</v>
       </c>
       <c r="M35">
-        <v>0.1827897386214441</v>
+        <v>0.1591320034239129</v>
       </c>
       <c r="N35">
-        <v>0.2210414580728384</v>
+        <v>0.1827897426149329</v>
       </c>
       <c r="O35">
-        <v>0.2228928739909924</v>
+        <v>0.2210414680281964</v>
       </c>
       <c r="P35">
-        <v>0.2565800981229915</v>
+        <v>0.2228926480871997</v>
+      </c>
+      <c r="Q35">
+        <v>0.2565800648282975</v>
       </c>
     </row>
     <row r="36">
@@ -2211,49 +2318,52 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.02023881578138964</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.03081182537576022</v>
+        <v>0.02023881576829289</v>
       </c>
       <c r="D36">
-        <v>0.07826815422334898</v>
+        <v>0.03081182538883875</v>
       </c>
       <c r="E36">
-        <v>0.06631148293204026</v>
+        <v>0.07826815366912521</v>
       </c>
       <c r="F36">
-        <v>0.0823325039124756</v>
+        <v>0.06631148279327093</v>
       </c>
       <c r="G36">
-        <v>0.1074029712225336</v>
+        <v>0.08233250304502182</v>
       </c>
       <c r="H36">
-        <v>0.1295384296352978</v>
+        <v>0.1074029695628561</v>
       </c>
       <c r="I36">
-        <v>0.1427013271685033</v>
+        <v>0.1295384279404115</v>
       </c>
       <c r="J36">
-        <v>0.1475882570168116</v>
+        <v>0.1427013293679273</v>
       </c>
       <c r="K36">
-        <v>0.1456273479212731</v>
+        <v>0.1475882567582458</v>
       </c>
       <c r="L36">
-        <v>0.1556827712226958</v>
+        <v>0.1456273493743384</v>
       </c>
       <c r="M36">
-        <v>0.1679721070164617</v>
+        <v>0.1556827746079</v>
       </c>
       <c r="N36">
-        <v>0.1992008300652812</v>
+        <v>0.1679720961788482</v>
       </c>
       <c r="O36">
-        <v>0.2046979749795537</v>
+        <v>0.1992008405057718</v>
       </c>
       <c r="P36">
-        <v>0.2272247498776424</v>
+        <v>0.2046979729342213</v>
+      </c>
+      <c r="Q36">
+        <v>0.2272247413362886</v>
       </c>
     </row>
     <row r="37">
@@ -2263,49 +2373,52 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.01714625030484351</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.04286033911237086</v>
+        <v>0.01714625031166617</v>
       </c>
       <c r="D37">
-        <v>0.0845413985245671</v>
+        <v>0.04286033825232982</v>
       </c>
       <c r="E37">
-        <v>0.1049310532260167</v>
+        <v>0.084541396812577</v>
       </c>
       <c r="F37">
-        <v>0.1664965062991327</v>
+        <v>0.1049310544000865</v>
       </c>
       <c r="G37">
-        <v>0.2353564354982173</v>
+        <v>0.1664965249335008</v>
       </c>
       <c r="H37">
-        <v>0.24508189405367</v>
+        <v>0.2353564728318404</v>
       </c>
       <c r="I37">
-        <v>0.2696097958777723</v>
+        <v>0.2450819011502258</v>
       </c>
       <c r="J37">
-        <v>0.2927500862530757</v>
+        <v>0.2696098035875625</v>
       </c>
       <c r="K37">
-        <v>0.3401689397269709</v>
+        <v>0.2927500361262534</v>
       </c>
       <c r="L37">
-        <v>0.3970999317909497</v>
+        <v>0.340168839031507</v>
       </c>
       <c r="M37">
-        <v>0.4650437323464031</v>
+        <v>0.3970996996931928</v>
       </c>
       <c r="N37">
-        <v>0.5661267147949427</v>
+        <v>0.4650463011124364</v>
       </c>
       <c r="O37">
-        <v>0.6305335170913522</v>
+        <v>0.5661281488745041</v>
       </c>
       <c r="P37">
-        <v>0.6930852089578196</v>
+        <v>0.6305332719670251</v>
+      </c>
+      <c r="Q37">
+        <v>0.6930849320160005</v>
       </c>
     </row>
     <row r="38">
@@ -2315,49 +2428,52 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.01894879783650438</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.03685986514368012</v>
+        <v>0.01894879784650705</v>
       </c>
       <c r="D38">
-        <v>0.06558438931071486</v>
+        <v>0.03685986472671121</v>
       </c>
       <c r="E38">
-        <v>0.07841477086454196</v>
+        <v>0.06558438835837355</v>
       </c>
       <c r="F38">
-        <v>0.1055666750852209</v>
+        <v>0.0784147711206421</v>
       </c>
       <c r="G38">
-        <v>0.1385830919341297</v>
+        <v>0.1055666750642135</v>
       </c>
       <c r="H38">
-        <v>0.1546729575616694</v>
+        <v>0.1385831016184385</v>
       </c>
       <c r="I38">
-        <v>0.207788627750457</v>
+        <v>0.1546729671436546</v>
       </c>
       <c r="J38">
-        <v>0.2844877081238915</v>
+        <v>0.2077886316889689</v>
       </c>
       <c r="K38">
-        <v>0.3463130798783871</v>
+        <v>0.2844877231031969</v>
       </c>
       <c r="L38">
-        <v>0.3792651943358073</v>
+        <v>0.346313105124827</v>
       </c>
       <c r="M38">
-        <v>0.3621608975065498</v>
+        <v>0.3792651743939567</v>
       </c>
       <c r="N38">
-        <v>0.3591546913990469</v>
+        <v>0.3621608765117184</v>
       </c>
       <c r="O38">
-        <v>0.3873868268243437</v>
+        <v>0.3591546019790778</v>
       </c>
       <c r="P38">
-        <v>0.415423679096049</v>
+        <v>0.3873866358755642</v>
+      </c>
+      <c r="Q38">
+        <v>0.4154235028280509</v>
       </c>
     </row>
     <row r="39">
@@ -2367,49 +2483,52 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.01841219200582167</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.03782117483614134</v>
+        <v>0.0184121920521958</v>
       </c>
       <c r="D39">
-        <v>0.06249407077320479</v>
+        <v>0.03782117453770417</v>
       </c>
       <c r="E39">
-        <v>0.07665054319223175</v>
+        <v>0.06249407065848334</v>
       </c>
       <c r="F39">
-        <v>0.1031161373950579</v>
+        <v>0.0766505427842199</v>
       </c>
       <c r="G39">
-        <v>0.1332803285254405</v>
+        <v>0.1031161356228409</v>
       </c>
       <c r="H39">
-        <v>0.1318977863543245</v>
+        <v>0.1332803339415675</v>
       </c>
       <c r="I39">
-        <v>0.1672246477307291</v>
+        <v>0.1318977885728232</v>
       </c>
       <c r="J39">
-        <v>0.2557080442762132</v>
+        <v>0.1672246514547834</v>
       </c>
       <c r="K39">
-        <v>0.2977159308785214</v>
+        <v>0.255708044401616</v>
       </c>
       <c r="L39">
-        <v>0.318301426072749</v>
+        <v>0.2977159301254173</v>
       </c>
       <c r="M39">
-        <v>0.3455678248454498</v>
+        <v>0.3183014252542194</v>
       </c>
       <c r="N39">
-        <v>0.3570423408923739</v>
+        <v>0.3455678322388326</v>
       </c>
       <c r="O39">
-        <v>0.3666960617645641</v>
+        <v>0.3570423348493126</v>
       </c>
       <c r="P39">
-        <v>0.4175437306723825</v>
+        <v>0.3666960293676242</v>
+      </c>
+      <c r="Q39">
+        <v>0.4175437118928327</v>
       </c>
     </row>
     <row r="40">
@@ -2419,49 +2538,52 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.02617432912804174</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.04759081798554277</v>
+        <v>0.02617432891754168</v>
       </c>
       <c r="D40">
-        <v>0.1090287766024982</v>
+        <v>0.04759081712611568</v>
       </c>
       <c r="E40">
-        <v>0.1092888085977682</v>
+        <v>0.109028774074203</v>
       </c>
       <c r="F40">
-        <v>0.1286027062062347</v>
+        <v>0.1092888029398226</v>
       </c>
       <c r="G40">
-        <v>0.176746185567731</v>
+        <v>0.1286027097431971</v>
       </c>
       <c r="H40">
-        <v>0.242257775603456</v>
+        <v>0.1767461916528135</v>
       </c>
       <c r="I40">
-        <v>0.298277346518429</v>
+        <v>0.2422577888817899</v>
       </c>
       <c r="J40">
-        <v>0.3335361392902754</v>
+        <v>0.2982773494265739</v>
       </c>
       <c r="K40">
-        <v>0.3663144003081769</v>
+        <v>0.3335360935082364</v>
       </c>
       <c r="L40">
-        <v>0.421163151575341</v>
+        <v>0.3663143213847969</v>
       </c>
       <c r="M40">
-        <v>0.5163345323784716</v>
+        <v>0.421163043332497</v>
       </c>
       <c r="N40">
-        <v>0.632528841868536</v>
+        <v>0.5163344098894327</v>
       </c>
       <c r="O40">
-        <v>0.7415477564839774</v>
+        <v>0.632528679919512</v>
       </c>
       <c r="P40">
-        <v>0.8025693375697041</v>
+        <v>0.7415474633328833</v>
+      </c>
+      <c r="Q40">
+        <v>0.8025689184115216</v>
       </c>
     </row>
     <row r="41">
@@ -2471,49 +2593,52 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.03161782145547021</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.05157383979085461</v>
+        <v>0.03161782124944168</v>
       </c>
       <c r="D41">
-        <v>0.1699489790214497</v>
+        <v>0.0515738393843469</v>
       </c>
       <c r="E41">
-        <v>0.2147884345347844</v>
+        <v>0.1699489775372063</v>
       </c>
       <c r="F41">
-        <v>0.2342525084049171</v>
+        <v>0.2147884327691316</v>
       </c>
       <c r="G41">
-        <v>0.3101283745457932</v>
+        <v>0.2342525023199914</v>
       </c>
       <c r="H41">
-        <v>0.3393160691683297</v>
+        <v>0.3101283602841733</v>
       </c>
       <c r="I41">
-        <v>0.3569585542092565</v>
+        <v>0.3393160384788954</v>
       </c>
       <c r="J41">
-        <v>0.3989731798145776</v>
+        <v>0.3569585132883485</v>
       </c>
       <c r="K41">
-        <v>0.4398258548446496</v>
+        <v>0.3989731236179659</v>
       </c>
       <c r="L41">
-        <v>0.5119037447328378</v>
+        <v>0.439825781061134</v>
       </c>
       <c r="M41">
-        <v>0.6251318060321897</v>
+        <v>0.5119036247640584</v>
       </c>
       <c r="N41">
-        <v>0.6745298648235388</v>
+        <v>0.6251316230189827</v>
       </c>
       <c r="O41">
-        <v>0.7239448462466471</v>
+        <v>0.6745296355298485</v>
       </c>
       <c r="P41">
-        <v>0.7597763628142187</v>
+        <v>0.7239445658718286</v>
+      </c>
+      <c r="Q41">
+        <v>0.7597760414079276</v>
       </c>
     </row>
     <row r="42">
@@ -2523,49 +2648,52 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.04215093774759604</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.04099427888624652</v>
+        <v>0.04215093737306896</v>
       </c>
       <c r="D42">
-        <v>0.1020285778412703</v>
+        <v>0.04099427832030977</v>
       </c>
       <c r="E42">
-        <v>0.2005775430591527</v>
+        <v>0.1020285757116526</v>
       </c>
       <c r="F42">
-        <v>0.2074590390947044</v>
+        <v>0.2005775352535007</v>
       </c>
       <c r="G42">
-        <v>0.2058009321605099</v>
+        <v>0.2074590392493324</v>
       </c>
       <c r="H42">
-        <v>0.2421257968570887</v>
+        <v>0.2058009388325114</v>
       </c>
       <c r="I42">
-        <v>0.3169510550180039</v>
+        <v>0.2421258079411874</v>
       </c>
       <c r="J42">
-        <v>0.4195410501682345</v>
+        <v>0.3169510458934034</v>
       </c>
       <c r="K42">
-        <v>0.4861341574596031</v>
+        <v>0.4195410627442457</v>
       </c>
       <c r="L42">
-        <v>0.5424382700906034</v>
+        <v>0.4861341835757588</v>
       </c>
       <c r="M42">
-        <v>0.5968380434276007</v>
+        <v>0.542438295907953</v>
       </c>
       <c r="N42">
-        <v>0.6296824837422634</v>
+        <v>0.5968381082969896</v>
       </c>
       <c r="O42">
-        <v>0.683487191627711</v>
+        <v>0.6296825669761454</v>
       </c>
       <c r="P42">
-        <v>0.7465284595094752</v>
+        <v>0.6834873060495938</v>
+      </c>
+      <c r="Q42">
+        <v>0.7465285795834089</v>
       </c>
     </row>
     <row r="43">
@@ -2575,49 +2703,52 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.02305367186670204</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.0717290488915332</v>
+        <v>0.02305367182535245</v>
       </c>
       <c r="D43">
-        <v>0.1191871567221819</v>
+        <v>0.07172904892504084</v>
       </c>
       <c r="E43">
-        <v>0.1341548657550802</v>
+        <v>0.1191871558693567</v>
       </c>
       <c r="F43">
-        <v>0.2071920291726627</v>
+        <v>0.1341548652599784</v>
       </c>
       <c r="G43">
-        <v>0.2325183224884243</v>
+        <v>0.207192030280911</v>
       </c>
       <c r="H43">
-        <v>0.2836957229409972</v>
+        <v>0.2325183252107659</v>
       </c>
       <c r="I43">
-        <v>0.3179998624180502</v>
+        <v>0.2836957257035829</v>
       </c>
       <c r="J43">
-        <v>0.3803570117690634</v>
+        <v>0.3179998593766964</v>
       </c>
       <c r="K43">
-        <v>0.467945269594372</v>
+        <v>0.3803570021032919</v>
       </c>
       <c r="L43">
-        <v>0.5446631581758561</v>
+        <v>0.4679452625582532</v>
       </c>
       <c r="M43">
-        <v>0.6084211007676888</v>
+        <v>0.5446631628494476</v>
       </c>
       <c r="N43">
-        <v>0.6384982924785105</v>
+        <v>0.6084211235224115</v>
       </c>
       <c r="O43">
-        <v>0.6536365342669687</v>
+        <v>0.6384983098004293</v>
       </c>
       <c r="P43">
-        <v>0.6772850501022272</v>
+        <v>0.6536365497316334</v>
+      </c>
+      <c r="Q43">
+        <v>0.6772850492040731</v>
       </c>
     </row>
   </sheetData>
